--- a/internal_doc/05.测试设计/自动化/现有用例排查_hxn_review.xlsx
+++ b/internal_doc/05.测试设计/自动化/现有用例排查_hxn_review.xlsx
@@ -731,7 +731,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="718">
   <si>
     <t>aggregate</t>
   </si>
@@ -8903,12 +8903,14 @@
         <v>169</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>83</v>
+        <v>540</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="F31" s="2"/>
+      <c r="F31" s="2" t="s">
+        <v>686</v>
+      </c>
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="1:7" ht="108">
@@ -8927,7 +8929,9 @@
       <c r="E32" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="F32" s="2"/>
+      <c r="F32" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="G32" s="2" t="s">
         <v>605</v>
       </c>
